--- a/data/trans_camb/P16A10-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,69</t>
+          <t>-0,33; 0,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,0</t>
+          <t>-0,82; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,0</t>
+          <t>-1,0; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,7</t>
+          <t>-0,4; 0,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,82</t>
+          <t>-0,4; 0,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,68</t>
+          <t>-0,4; 4,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,56</t>
+          <t>-0,35; 0,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,28</t>
+          <t>-0,37; 0,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,68</t>
+          <t>-0,28; 1,51</t>
         </is>
       </c>
     </row>
@@ -893,42 +893,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>-0,12; 1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,31</t>
+          <t>-0,13; 1,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,0</t>
+          <t>-0,64; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,31</t>
+          <t>-0,72; 0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,89</t>
+          <t>0,04; 1,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,3</t>
+          <t>-0,41; 1,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,75</t>
+          <t>-0,19; 0,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,19</t>
+          <t>0,06; 1,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,86; —</t>
+          <t>-45,26; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,19; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,0; —</t>
+          <t>-10,68; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,88</t>
+          <t>-0,86; 1,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,29</t>
+          <t>-1,28; 0,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,29</t>
+          <t>-0,96; 1,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,53</t>
+          <t>-0,87; 1,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,83</t>
+          <t>-1,45; 0,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,49</t>
+          <t>-1,61; 0,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,89</t>
+          <t>-0,54; 0,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,3</t>
+          <t>-1,04; 0,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,52</t>
+          <t>-1,01; 0,47</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 300,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 267,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 461,14</t>
+          <t>-100,0; 562,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 239,61</t>
+          <t>-56,74; 252,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,26; 165,67</t>
+          <t>-78,66; 148,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,34; 115,88</t>
+          <t>-85,12; 117,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 165,82</t>
+          <t>-46,64; 175,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,21; 73,95</t>
+          <t>-76,9; 61,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 92,62</t>
+          <t>-75,61; 94,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,61</t>
+          <t>-2,28; 1,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,52</t>
+          <t>-1,4; 2,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,48</t>
+          <t>-2,05; 2,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,51</t>
+          <t>-4,19; -0,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,79</t>
+          <t>-3,45; 0,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; -0,37</t>
+          <t>-3,77; -0,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,22</t>
+          <t>-2,39; 0,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,07</t>
+          <t>-1,75; 1,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,66</t>
+          <t>-2,34; 0,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 119,76</t>
+          <t>-64,52; 118,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,35; 172,8</t>
+          <t>-44,37; 156,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 140,2</t>
+          <t>-54,81; 156,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,26; -13,84</t>
+          <t>-88,68; -8,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 45,13</t>
+          <t>-69,63; 43,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,31; -13,62</t>
+          <t>-79,03; -6,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,14; 12,19</t>
+          <t>-65,6; 22,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 49,99</t>
+          <t>-46,56; 57,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 28,43</t>
+          <t>-60,64; 32,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 1,54</t>
+          <t>-7,0; 1,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 3,57</t>
+          <t>-4,86; 3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -0,09</t>
+          <t>-7,19; 0,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,21</t>
+          <t>-3,32; 3,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,18; -0,53</t>
+          <t>-6,63; -0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,78</t>
+          <t>-4,48; 1,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,36</t>
+          <t>-3,95; 1,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,81</t>
+          <t>-4,6; 0,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,29</t>
+          <t>-4,84; -0,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 16,64</t>
+          <t>-50,46; 19,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 40,62</t>
+          <t>-36,24; 45,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -0,94</t>
+          <t>-54,12; 1,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 70,95</t>
+          <t>-43,39; 65,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,19; -5,21</t>
+          <t>-78,86; -10,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,78; 17,78</t>
+          <t>-54,58; 28,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 20,8</t>
+          <t>-39,92; 15,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 12,07</t>
+          <t>-45,35; 10,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-48,62; -3,5</t>
+          <t>-48,37; -5,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 3,51</t>
+          <t>-8,5; 3,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 8,86</t>
+          <t>-3,68; 8,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 0,31</t>
+          <t>-10,18; 0,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 0,81</t>
+          <t>-9,54; 0,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 4,23</t>
+          <t>-6,97; 3,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -5,48</t>
+          <t>-16,97; -5,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 0,62</t>
+          <t>-7,63; 0,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 4,23</t>
+          <t>-3,73; 4,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -4,53</t>
+          <t>-13,49; -4,52</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 25,31</t>
+          <t>-40,84; 26,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 59,28</t>
+          <t>-18,0; 62,28</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 3,04</t>
+          <t>-47,6; 3,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-53,7; 6,87</t>
+          <t>-53,92; 0,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 37,79</t>
+          <t>-39,08; 28,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-86,49; -40,5</t>
+          <t>-87,0; -40,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 4,93</t>
+          <t>-41,79; 1,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 29,88</t>
+          <t>-20,3; 33,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-75,48; -31,96</t>
+          <t>-74,71; -30,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 8,35</t>
+          <t>-9,5; 8,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 0,89</t>
+          <t>-14,45; 1,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 0,72</t>
+          <t>-14,11; 0,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 6,23</t>
+          <t>-6,29; 6,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 8,95</t>
+          <t>-4,94; 9,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,47</t>
+          <t>-4,75; 6,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 4,75</t>
+          <t>-5,51; 4,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 3,72</t>
+          <t>-6,17; 4,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 2,62</t>
+          <t>-6,27; 2,88</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 32,28</t>
+          <t>-27,51; 32,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 3,63</t>
+          <t>-40,82; 6,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 2,67</t>
+          <t>-39,74; 2,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 33,89</t>
+          <t>-24,68; 37,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 47,93</t>
+          <t>-18,6; 46,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 39,89</t>
+          <t>-17,45; 36,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 20,9</t>
+          <t>-19,29; 21,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 16,54</t>
+          <t>-21,62; 17,86</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 11,89</t>
+          <t>-21,89; 12,92</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,01</t>
+          <t>-1,17; 1,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,62</t>
+          <t>-0,64; 1,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,06</t>
+          <t>-1,56; 1,07</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,53</t>
+          <t>-1,54; 0,61</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,17</t>
+          <t>-0,99; 1,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,57</t>
+          <t>-1,58; 0,57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,46</t>
+          <t>-1,03; 0,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,16</t>
+          <t>-0,48; 1,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,59</t>
+          <t>-1,04; 0,64</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 21,11</t>
+          <t>-19,8; 21,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 34,73</t>
+          <t>-10,95; 32,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 21,54</t>
+          <t>-27,05; 21,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 11,11</t>
+          <t>-26,0; 13,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 23,83</t>
+          <t>-17,16; 26,76</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 11,78</t>
+          <t>-27,0; 12,23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 9,16</t>
+          <t>-18,15; 9,24</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 23,62</t>
+          <t>-8,42; 22,24</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 11,46</t>
+          <t>-18,23; 12,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A10-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Edad-trans_camb.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,66</t>
+          <t>-0,33; 0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,0</t>
+          <t>-0,84; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,0</t>
+          <t>-0,83; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,82</t>
+          <t>-0,4; 0,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,78</t>
+          <t>-0,41; 0,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,09</t>
+          <t>-0,4; 3,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,46</t>
+          <t>-0,34; 0,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,29</t>
+          <t>-0,38; 0,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,51</t>
+          <t>-0,28; 1,89</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>325,44%</t>
+          <t>323,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105,03%</t>
+          <t>118,47%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>-0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,39</t>
+          <t>-0,09; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,22</t>
+          <t>-0,13; 1,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,0</t>
+          <t>-0,71; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,31</t>
+          <t>-0,7; 0,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,89</t>
+          <t>-0,08; 1,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,4</t>
+          <t>-0,43; 1,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,7</t>
+          <t>-0,2; 0,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,2</t>
+          <t>0,05; 1,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,69</t>
+          <t>-0,31; 0,4</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>-1,73%</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,26; —</t>
+          <t>-71,25; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,19; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,68; —</t>
+          <t>-19,07; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,0</t>
+          <t>-0,98; 0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,17</t>
+          <t>-1,3; 0,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,04</t>
+          <t>-0,97; 0,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,51</t>
+          <t>-0,96; 1,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,68</t>
+          <t>-1,37; 0,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,49</t>
+          <t>-1,71; 0,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,99</t>
+          <t>-0,66; 0,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,27</t>
+          <t>-1,07; 0,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,47</t>
+          <t>-0,94; 0,47</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-3,1%</t>
+          <t>-15,51%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-37,47%</t>
+          <t>-37,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-24,57%</t>
+          <t>-29,17%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-86,73; 264,58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 562,66</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 252,22</t>
+          <t>-59,5; 258,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,66; 148,86</t>
+          <t>-77,09; 181,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,12; 117,13</t>
+          <t>-82,83; 102,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 175,2</t>
+          <t>-51,6; 167,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 61,35</t>
+          <t>-80,69; 57,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,61; 94,95</t>
+          <t>-74,84; 108,66</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,59</t>
+          <t>-2,19; 1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,47</t>
+          <t>-1,56; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,62</t>
+          <t>-0,65; 3,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; -0,43</t>
+          <t>-4,34; -0,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,71</t>
+          <t>-3,42; 0,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; -0,26</t>
+          <t>-3,71; -0,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,39</t>
+          <t>-2,48; 0,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,19</t>
+          <t>-1,67; 1,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,71</t>
+          <t>-1,66; 1,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-56,1%</t>
+          <t>-52,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-21,89%</t>
+          <t>-5,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,52; 118,22</t>
+          <t>-62,53; 128,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 156,72</t>
+          <t>-44,59; 165,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,81; 156,93</t>
+          <t>-22,64; 206,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-88,68; -8,89</t>
+          <t>-88,09; -10,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,63; 43,66</t>
+          <t>-71,29; 37,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,03; -6,28</t>
+          <t>-77,32; 0,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,6; 22,55</t>
+          <t>-67,51; 8,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 57,24</t>
+          <t>-45,93; 55,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 32,21</t>
+          <t>-43,81; 51,56</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,58</t>
+          <t>-3,49</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 1,57</t>
+          <t>-6,81; 1,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,78</t>
+          <t>-5,09; 3,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 0,1</t>
+          <t>-7,17; 0,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,04</t>
+          <t>-3,64; 3,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -0,72</t>
+          <t>-6,39; -0,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,0</t>
+          <t>-4,43; 0,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,09</t>
+          <t>-4,13; 1,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,69</t>
+          <t>-4,3; 0,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -0,45</t>
+          <t>-4,58; 0,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-32,35%</t>
+          <t>-31,5%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,71%</t>
+          <t>-25,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-30,0%</t>
+          <t>-28,88%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 19,74</t>
+          <t>-51,84; 17,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 45,55</t>
+          <t>-37,75; 40,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 1,67</t>
+          <t>-51,62; 4,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 65,36</t>
+          <t>-44,25; 76,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-78,86; -10,75</t>
+          <t>-76,66; -3,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,58; 28,34</t>
+          <t>-53,17; 25,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 15,38</t>
+          <t>-40,7; 15,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,35; 10,38</t>
+          <t>-43,63; 11,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-48,37; -5,96</t>
+          <t>-47,04; 0,31</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-4,63</t>
+          <t>-5,09</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-9,67</t>
+          <t>-6,75</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-7,98</t>
+          <t>-5,9</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 3,69</t>
+          <t>-8,09; 3,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 8,57</t>
+          <t>-3,9; 8,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 0,35</t>
+          <t>-10,4; -0,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 0,05</t>
+          <t>-9,18; 0,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,43</t>
+          <t>-6,62; 3,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -5,63</t>
+          <t>-11,43; -2,74</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 0,24</t>
+          <t>-7,46; 0,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 4,61</t>
+          <t>-3,88; 4,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -4,52</t>
+          <t>-9,19; -2,56</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-26,39%</t>
+          <t>-28,95%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-64,3%</t>
+          <t>-44,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-49,27%</t>
+          <t>-36,41%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 26,75</t>
+          <t>-40,55; 25,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 62,28</t>
+          <t>-18,58; 57,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 3,23</t>
+          <t>-49,41; 0,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 0,48</t>
+          <t>-53,22; 4,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 28,56</t>
+          <t>-37,79; 28,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-87,0; -40,12</t>
+          <t>-61,42; -21,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 1,85</t>
+          <t>-40,83; 0,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 33,04</t>
+          <t>-21,32; 28,16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,71; -30,45</t>
+          <t>-49,84; -18,11</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-5,98</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,02</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 8,5</t>
+          <t>-8,91; 8,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 1,43</t>
+          <t>-14,26; 0,91</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 0,69</t>
+          <t>-13,26; 1,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 6,86</t>
+          <t>-6,6; 6,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 9,12</t>
+          <t>-4,93; 9,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,81</t>
+          <t>-3,59; 7,72</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,92</t>
+          <t>-5,11; 4,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,06</t>
+          <t>-6,68; 4,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,88</t>
+          <t>-5,19; 3,19</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-21,76%</t>
+          <t>-19,66%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-5,48%</t>
+          <t>-4,01%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 32,11</t>
+          <t>-26,08; 34,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 6,62</t>
+          <t>-40,86; 3,26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 2,79</t>
+          <t>-37,55; 7,25</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 37,1</t>
+          <t>-24,97; 36,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 46,27</t>
+          <t>-18,21; 48,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 36,59</t>
+          <t>-13,67; 42,11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 21,64</t>
+          <t>-18,66; 21,28</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 17,86</t>
+          <t>-23,65; 18,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 12,92</t>
+          <t>-18,2; 14,41</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,04</t>
+          <t>-1,28; 1,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,59</t>
+          <t>-0,63; 1,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,07</t>
+          <t>-0,75; 1,34</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,61</t>
+          <t>-1,6; 0,55</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,26</t>
+          <t>-1,08; 1,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,57</t>
+          <t>-1,02; 0,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,46</t>
+          <t>-1,0; 0,49</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,11</t>
+          <t>-0,42; 1,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,64</t>
+          <t>-0,53; 0,94</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-0,36%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-7,3%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-3,9%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 21,89</t>
+          <t>-21,4; 20,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 32,54</t>
+          <t>-10,59; 33,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 21,93</t>
+          <t>-12,14; 27,12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 13,5</t>
+          <t>-27,38; 11,94</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 26,76</t>
+          <t>-18,71; 24,56</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 12,23</t>
+          <t>-16,84; 19,6</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 9,24</t>
+          <t>-17,56; 9,7</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 22,24</t>
+          <t>-7,41; 22,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 12,94</t>
+          <t>-9,27; 19,29</t>
         </is>
       </c>
     </row>
